--- a/presupuesto_TMK.xlsx
+++ b/presupuesto_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/02 Febrero/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/05 Mayo/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="11_E95008F7534E980F6235547658484EBB89F0B472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DD27E66-F025-488E-A9FB-9D54DD663D8E}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="11_E95008F7534E980F6235547658484EBB89F0B472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A133488-0260-4102-A57D-47A876C76FAB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,13 @@
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$I$51</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="25">
   <si>
     <t>Año</t>
   </si>
@@ -71,37 +74,46 @@
     <t>Venta directa - salarial</t>
   </si>
   <si>
+    <t>Líder</t>
+  </si>
+  <si>
+    <t>Maria Deisy Gil Gomez</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>Referido - bono</t>
+  </si>
+  <si>
+    <t>Pyme Móvil - salarial</t>
+  </si>
+  <si>
+    <t>CLOUND - salarial</t>
+  </si>
+  <si>
     <t>Auxiliar</t>
   </si>
   <si>
     <t>Natalia  Giraldo Galeano</t>
   </si>
   <si>
-    <t>0%</t>
-  </si>
-  <si>
     <t>Raiza Lorena Urzola Lora</t>
   </si>
   <si>
     <t>Yessica Yulieth Moreno</t>
   </si>
   <si>
-    <t>Referido - bono</t>
-  </si>
-  <si>
-    <t>Líder</t>
-  </si>
-  <si>
-    <t>Maria Deisy Gil Gomez</t>
-  </si>
-  <si>
-    <t>Pyme Móvil - salarial</t>
-  </si>
-  <si>
-    <t>CLOUND - salarial</t>
-  </si>
-  <si>
     <t>Febrero</t>
+  </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Mayo</t>
   </si>
 </sst>
 </file>
@@ -170,7 +182,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -180,6 +192,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,12 +496,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -539,13 +553,13 @@
         <v>12</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>26.5</v>
       </c>
       <c r="H2">
-        <v>1.1000000000000001</v>
+        <v>0.442</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -559,22 +573,22 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>0.05</v>
+        <v>186</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1.2333333333333334</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
@@ -588,22 +602,22 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>0.15</v>
+        <v>14</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
@@ -625,14 +639,14 @@
       <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F5">
-        <v>40</v>
-      </c>
-      <c r="G5" s="2">
-        <v>63</v>
+      <c r="F5" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G5" s="4">
+        <v>215424</v>
       </c>
       <c r="H5" s="3">
-        <v>1.575</v>
+        <v>0</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
@@ -646,22 +660,22 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>40</v>
-      </c>
-      <c r="G6" s="2">
-        <v>75</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1.875</v>
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>1.1000000000000001</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
@@ -675,22 +689,22 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>40</v>
       </c>
       <c r="G7" s="2">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H7" s="3">
-        <v>1.175</v>
+        <v>1.575</v>
       </c>
       <c r="I7" t="s">
         <v>13</v>
@@ -710,16 +724,16 @@
         <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G8">
-        <v>26.5</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0.442</v>
+        <v>0.05</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
@@ -733,22 +747,22 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>150</v>
-      </c>
-      <c r="G9">
-        <v>185</v>
+        <v>40</v>
+      </c>
+      <c r="G9" s="2">
+        <v>75</v>
       </c>
       <c r="H9" s="3">
-        <v>1.2333333333333334</v>
+        <v>1.875</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
@@ -762,22 +776,22 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G10">
-        <v>14</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>0.15</v>
       </c>
       <c r="I10" t="s">
         <v>13</v>
@@ -791,22 +805,22 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
       <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="G11" s="2">
+        <v>47</v>
       </c>
       <c r="H11" s="3">
-        <v>0</v>
+        <v>1.175</v>
       </c>
       <c r="I11" t="s">
         <v>13</v>
@@ -829,14 +843,14 @@
         <v>12</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G12">
-        <v>24</v>
+        <v>60.5</v>
       </c>
       <c r="H12" s="3">
-        <f>G12/F12</f>
-        <v>0.96</v>
+        <f t="shared" ref="H12:H21" si="0">G12/F12</f>
+        <v>0.80666666666666664</v>
       </c>
       <c r="I12" t="s">
         <v>13</v>
@@ -850,7 +864,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -859,14 +873,14 @@
         <v>12</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G13">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" ref="H13:H21" si="0">G13/F13</f>
-        <v>1.22</v>
+        <f t="shared" si="0"/>
+        <v>1.1333333333333333</v>
       </c>
       <c r="I13" t="s">
         <v>13</v>
@@ -880,23 +894,23 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G14">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>0.68</v>
+        <v>0.05</v>
       </c>
       <c r="I14" t="s">
         <v>13</v>
@@ -916,204 +930,1044 @@
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G15" s="4">
+        <v>511000</v>
+      </c>
+      <c r="H15" s="3">
+        <f>G5/F15</f>
+        <v>2.1542400000000002</v>
+      </c>
+      <c r="I15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2026</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16">
+        <v>25</v>
+      </c>
+      <c r="G16">
+        <v>24</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2026</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17">
         <v>50</v>
       </c>
-      <c r="G15">
+      <c r="G17">
+        <v>61</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="0"/>
+        <v>1.22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18">
+        <v>25</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.68</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2026</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19">
+        <v>50</v>
+      </c>
+      <c r="G19">
         <v>58</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H19" s="3">
         <f t="shared" si="0"/>
         <v>1.1599999999999999</v>
       </c>
-      <c r="I15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2026</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2026</v>
+      </c>
+      <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16">
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20">
         <v>25</v>
       </c>
-      <c r="G16">
-        <v>13</v>
-      </c>
-      <c r="H16" s="3">
+      <c r="G20">
+        <v>13</v>
+      </c>
+      <c r="H20" s="3">
         <f t="shared" si="0"/>
         <v>0.52</v>
       </c>
-      <c r="I16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2026</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="s">
         <v>21</v>
       </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17">
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21">
         <v>50</v>
       </c>
-      <c r="G17">
+      <c r="G21">
         <v>52</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H21" s="3">
         <f t="shared" si="0"/>
         <v>1.04</v>
       </c>
-      <c r="I17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2026</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2026</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>75</v>
+      </c>
+      <c r="G22">
+        <v>46</v>
+      </c>
+      <c r="H22" s="3">
+        <f>G22/F22</f>
+        <v>0.61333333333333329</v>
+      </c>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2026</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>150</v>
+      </c>
+      <c r="G23">
+        <v>169</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" ref="H23:H31" si="1">G23/F23</f>
+        <v>1.1266666666666667</v>
+      </c>
+      <c r="I23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2026</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>60</v>
+      </c>
+      <c r="G24">
+        <v>11</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="1"/>
+        <v>0.18333333333333332</v>
+      </c>
+      <c r="I24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2026</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2026</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
         <v>18</v>
       </c>
-      <c r="F18">
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+      <c r="I26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>33</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="1"/>
+        <v>1.375</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2026</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28">
+        <v>19</v>
+      </c>
+      <c r="G28">
+        <v>18</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="1"/>
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2026</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29">
+        <v>38</v>
+      </c>
+      <c r="G29">
+        <v>57</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="I29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2026</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30">
+        <v>25</v>
+      </c>
+      <c r="G30">
+        <v>14</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="1"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2026</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31">
+        <v>50</v>
+      </c>
+      <c r="G31">
+        <v>79</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="1"/>
+        <v>1.58</v>
+      </c>
+      <c r="I31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2026</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
         <v>75</v>
       </c>
-      <c r="G18">
-        <v>60.5</v>
-      </c>
-      <c r="H18" s="3">
-        <f t="shared" si="0"/>
-        <v>0.80666666666666664</v>
-      </c>
-      <c r="I18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2026</v>
-      </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="G32">
+        <v>52.5</v>
+      </c>
+      <c r="H32" s="3">
+        <f>G32/F32</f>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2026</v>
+      </c>
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33">
+        <v>150</v>
+      </c>
+      <c r="G33">
+        <v>163</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" ref="H33:H41" si="2">G33/F33</f>
+        <v>1.0866666666666667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2026</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34">
+        <v>60</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2026</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
         <v>16</v>
       </c>
-      <c r="D19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G35" s="4">
+        <v>2153085</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="2"/>
+        <v>21.530850000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2026</v>
+      </c>
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s">
         <v>18</v>
       </c>
-      <c r="F19">
+      <c r="F36">
+        <v>25</v>
+      </c>
+      <c r="G36">
+        <v>16</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="2"/>
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2026</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37">
+        <v>50</v>
+      </c>
+      <c r="G37">
+        <v>51</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="2"/>
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2026</v>
+      </c>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38">
+        <v>25</v>
+      </c>
+      <c r="G38">
+        <v>22</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="2"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2026</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39">
+        <v>50</v>
+      </c>
+      <c r="G39">
+        <v>57</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2026</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40">
+        <v>25</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2026</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41">
+        <v>50</v>
+      </c>
+      <c r="G41">
+        <v>50</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2026</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42">
+        <v>75</v>
+      </c>
+      <c r="G42">
+        <v>75.5</v>
+      </c>
+      <c r="H42" s="5">
+        <f>G42/F42</f>
+        <v>1.0066666666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2026</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43">
         <v>150</v>
       </c>
-      <c r="G19">
-        <v>170</v>
-      </c>
-      <c r="H19" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
-      </c>
-      <c r="I19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2026</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="G43">
+        <v>174</v>
+      </c>
+      <c r="H43" s="5">
+        <f t="shared" ref="H43:H45" si="3">G43/F43</f>
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2026</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44">
+        <v>60</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2026</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G45" s="4">
+        <v>259090</v>
+      </c>
+      <c r="H45" s="5">
+        <f t="shared" si="3"/>
+        <v>2.5909</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46">
+        <v>25</v>
+      </c>
+      <c r="G46">
+        <v>18</v>
+      </c>
+      <c r="H46" s="5">
+        <f>G46/F46</f>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="G47">
+        <v>52</v>
+      </c>
+      <c r="H47" s="5">
+        <f t="shared" ref="H47:H51" si="4">G47/F47</f>
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" t="s">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20">
-        <v>60</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
-        <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="I20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2026</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="F48">
+        <v>25</v>
+      </c>
+      <c r="G48">
+        <v>19</v>
+      </c>
+      <c r="H48" s="5">
+        <f t="shared" si="4"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2026</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49">
+        <v>50</v>
+      </c>
+      <c r="G49">
+        <v>57</v>
+      </c>
+      <c r="H49" s="5">
+        <f t="shared" si="4"/>
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2026</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" t="s">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="4">
-        <v>100000</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" t="s">
-        <v>13</v>
+      <c r="F50">
+        <v>25</v>
+      </c>
+      <c r="G50">
+        <v>20</v>
+      </c>
+      <c r="H50" s="5">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2026</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51">
+        <v>50</v>
+      </c>
+      <c r="G51">
+        <v>65</v>
+      </c>
+      <c r="H51" s="5">
+        <f t="shared" si="4"/>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>